--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U267"/>
+  <dimension ref="A1:U271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23447,12 +23447,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Cerro Maggiore</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -23472,12 +23472,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Cerro Maggiore</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -23487,11 +23487,11 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J229" t="n">
-        <v>40.31</v>
+        <v>12.364</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -23508,32 +23508,32 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA LEONE XIII 14</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
@@ -23548,12 +23548,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -23578,7 +23578,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>14.528</v>
+        <v>40.31</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -23609,32 +23609,32 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
@@ -23649,12 +23649,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -23664,7 +23664,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Scaldasole 41</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Scaldasole</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -23693,7 +23693,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>37.16</v>
+        <v>14.528</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -23710,17 +23710,17 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -23750,12 +23750,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -23765,22 +23765,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>PV Alessandria</t>
+          <t>Scaldasole 41</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Scaldasole</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -23794,7 +23794,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>5</v>
+        <v>37.16</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -23806,37 +23806,37 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>PV Tortona</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Tortona</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -23895,7 +23895,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -23907,7 +23907,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -23952,12 +23952,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -23967,22 +23967,22 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>PV Bissina</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Santa Cristina e Bissone</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>78.46299999999999</v>
+        <v>10</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -24013,32 +24013,32 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
@@ -24053,12 +24053,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Cascina Grande</t>
+          <t>PV Bissina</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dorno</t>
+          <t>Santa Cristina e Bissone</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>121.697</v>
+        <v>78.46299999999999</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -24114,32 +24114,32 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>VIA GIOSUE' CARDUCCI 8</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
@@ -24154,12 +24154,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -24169,36 +24169,36 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Cascina Grande</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Dorno</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J236" t="n">
-        <v>48.5</v>
+        <v>121.697</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -24215,27 +24215,27 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA GIOSUE' CARDUCCI 8</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>TRIESTE</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -24280,12 +24280,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -24299,7 +24299,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -24356,12 +24356,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -24417,17 +24417,17 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -24457,12 +24457,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -24472,7 +24472,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -24487,7 +24487,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -24501,7 +24501,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -24518,27 +24518,27 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
@@ -24558,12 +24558,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -24602,7 +24602,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>29.73</v>
+        <v>36.32</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -24619,27 +24619,27 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
@@ -24659,12 +24659,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>PV Villadose</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -24689,7 +24689,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Villadose</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -24703,7 +24703,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>37.481</v>
+        <v>29.73</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -24720,32 +24720,32 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
@@ -24760,12 +24760,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>CASTELNOVO B.</t>
+          <t>PV Villadose</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Castelnovo Bariano</t>
+          <t>Villadose</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -24804,7 +24804,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>15.03</v>
+        <v>37.481</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -24821,32 +24821,32 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>VIA VARESE 194</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
@@ -24861,12 +24861,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Bagnoli 1, 2, 3, 4</t>
+          <t>CASTELNOVO B.</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -24886,26 +24886,26 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
+          <t>Rovigo</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Castelnovo Bariano</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
           <t>Padova</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Bagnoli di Sopra</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>Padova</t>
-        </is>
-      </c>
       <c r="J243" t="n">
-        <v>26.67</v>
+        <v>15.03</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -24922,7 +24922,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>VIA VARESE 194</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
@@ -24962,12 +24962,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -24977,7 +24977,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>PV via Murazze snc</t>
+          <t>Bagnoli 1, 2, 3, 4</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -24987,12 +24987,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Porto Viro</t>
+          <t>Bagnoli di Sopra</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>19.56</v>
+        <v>26.67</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -25063,12 +25063,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -25078,7 +25078,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>PV Ariano nel Polese</t>
+          <t>PV via Murazze snc</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Ariano nel Polesine</t>
+          <t>Porto Viro</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -25107,7 +25107,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>19.09</v>
+        <v>19.56</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -25124,7 +25124,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>VIA GIANFRANCO MALIPIERO 16-18</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -25134,7 +25134,7 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -25164,88 +25164,88 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV Ariano nel Polese</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Ariano nel Polesine</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J246" t="n">
-        <v>7</v>
+        <v>19.09</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIA GIANFRANCO MALIPIERO 16-18</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
@@ -25265,12 +25265,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -25280,36 +25280,36 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Stienta</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Stienta</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J247" t="n">
-        <v>72</v>
+        <v>117.9</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -25326,17 +25326,17 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA FELICE CAVALLOTTI 13</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
@@ -25366,12 +25366,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -25381,36 +25381,36 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>FABBRICO</t>
+          <t>PV Guarda Veneta</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Fabbrico</t>
+          <t>Guarda Veneta</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J248" t="n">
-        <v>16.806</v>
+        <v>32.008</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -25427,27 +25427,27 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>VIA ANTONIO ANDREUZZI 12</t>
+          <t>PIAZZALE LUIGI CADORNA 6</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
@@ -25467,22 +25467,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -25492,12 +25492,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -25511,44 +25511,44 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>VIA FERSINA 23</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>TRENTO</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
@@ -25568,12 +25568,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -25583,7 +25583,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Casella</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -25593,12 +25593,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Castel San Giovanni</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -25612,7 +25612,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>14.49</v>
+        <v>72</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -25629,17 +25629,17 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>PIAZZA BORROMEO 14</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
@@ -25649,7 +25649,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
@@ -25669,12 +25669,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -25684,36 +25684,36 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>FABBRICO</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Fabbrico</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J251" t="n">
-        <v>19.88</v>
+        <v>16.806</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -25730,27 +25730,27 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO ANDREUZZI 12</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -25770,12 +25770,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -25785,36 +25785,36 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J252" t="n">
-        <v>19.96</v>
+        <v>20</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -25826,32 +25826,32 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA FERSINA 23</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TRENTO</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -25871,12 +25871,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -25886,36 +25886,36 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>Casella</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Castel San Giovanni</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J253" t="n">
-        <v>22.925</v>
+        <v>14.49</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -25932,27 +25932,27 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>PIAZZA BORROMEO 14</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
@@ -25972,12 +25972,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -25987,7 +25987,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>19.968</v>
+        <v>19.88</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -26033,27 +26033,27 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
@@ -26073,12 +26073,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -26088,7 +26088,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -26134,27 +26134,27 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -26174,88 +26174,88 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
+          <t>Potenza</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Melfi</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Salerno</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>22.925</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>VIA LUIGI BUZZI 6</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>CASALE MONFERRATO</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
           <t>Torino</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>Pinerolo</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Nord Ovest</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="J256" t="n">
-        <v>12</v>
-      </c>
-      <c r="K256" t="n">
-        <v>1</v>
-      </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>Attivo</t>
-        </is>
-      </c>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>Costruzione</t>
-        </is>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>VIA MATTATOIO 3</t>
-        </is>
-      </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>SALUZZO</t>
-        </is>
-      </c>
-      <c r="P256" t="inlineStr">
-        <is>
-          <t>12037</t>
-        </is>
-      </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="R256" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
@@ -26275,12 +26275,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -26290,36 +26290,36 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J257" t="n">
-        <v>46.7235</v>
+        <v>19.968</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -26336,17 +26336,17 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
@@ -26376,12 +26376,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -26391,36 +26391,36 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J258" t="n">
-        <v>2</v>
+        <v>19.96</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -26437,27 +26437,27 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
@@ -26477,22 +26477,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -26507,7 +26507,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -26521,44 +26521,44 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>18.774</v>
+        <v>12</v>
       </c>
       <c r="K259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
@@ -26578,22 +26578,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -26603,12 +26603,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>18</v>
+        <v>46.7235</v>
       </c>
       <c r="K260" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -26634,32 +26634,32 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
@@ -26679,12 +26679,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -26694,36 +26694,36 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J261" t="n">
-        <v>96.09</v>
+        <v>2</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -26740,27 +26740,27 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -26780,12 +26780,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -26795,36 +26795,36 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>GREENFRUT</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Bicinicco</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J262" t="n">
-        <v>68.51000000000001</v>
+        <v>18.774</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -26841,32 +26841,32 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>BICINICCO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
@@ -26881,54 +26881,54 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J263" t="n">
-        <v>20.787</v>
+        <v>18</v>
       </c>
       <c r="K263" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -26937,32 +26937,32 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
@@ -26982,12 +26982,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -26997,22 +26997,22 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -27022,11 +27022,11 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J264" t="n">
-        <v>27.867</v>
+        <v>96.09</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -27043,27 +27043,27 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
@@ -27083,12 +27083,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -27098,36 +27098,36 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>GREENFRUT</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Bicinicco</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>18.419</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -27144,27 +27144,27 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>VIA ALDO MORO 233</t>
+          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>FROSINONE</t>
+          <t>BICINICCO</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>33050</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
@@ -27184,12 +27184,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -27199,36 +27199,36 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J266" t="n">
-        <v>28.61</v>
+        <v>20.787</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -27245,27 +27245,27 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>PIAZZA CASTELLO 19</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
@@ -27285,12 +27285,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -27300,36 +27300,36 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Prato Smeraldo</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J267" t="n">
-        <v>8.891999999999999</v>
+        <v>27.867</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -27346,40 +27346,444 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
+          <t>VIA BIGLI 2</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>PV Cavarzere</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Cavarzere</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>PIAZZA CAVOUR 17</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>VIA ALDO MORO 233</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>FROSINONE</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>STESSA FILIALE</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Latina Fondazione</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>PIAZZA CASTELLO 19</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Prato Smeraldo</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>8.891999999999999</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
           <t>VIALE CASTRENSE 9</t>
         </is>
       </c>
-      <c r="O267" t="inlineStr">
+      <c r="O271" t="inlineStr">
         <is>
           <t>ROMA</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr">
+      <c r="P271" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr">
+      <c r="Q271" t="inlineStr">
         <is>
           <t>RM</t>
         </is>
       </c>
-      <c r="R267" t="inlineStr">
+      <c r="R271" t="inlineStr">
         <is>
           <t>Roma Aurelia</t>
         </is>
       </c>
-      <c r="S267" t="inlineStr">
+      <c r="S271" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T267" t="inlineStr">
+      <c r="T271" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U267" t="n">
+      <c r="U271" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27394,7 +27798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U232"/>
+  <dimension ref="A1:U235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48814,88 +49218,88 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV Stienta</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Stienta</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J213" t="n">
-        <v>7</v>
+        <v>117.9</v>
       </c>
       <c r="K213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIA FELICE CAVALLOTTI 13</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
@@ -48915,12 +49319,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -48930,36 +49334,36 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Guarda Veneta</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Guarda Veneta</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J214" t="n">
-        <v>72</v>
+        <v>32.008</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -48976,17 +49380,17 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>PIAZZALE LUIGI CADORNA 6</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
@@ -48996,7 +49400,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
@@ -49016,22 +49420,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>FABBRICO</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -49041,12 +49445,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Fabbrico</t>
+          <t>Podenzano</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -49060,44 +49464,44 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>16.806</v>
+        <v>7</v>
       </c>
       <c r="K215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>VIA ANTONIO ANDREUZZI 12</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
@@ -49117,12 +49521,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -49132,7 +49536,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -49142,12 +49546,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -49161,7 +49565,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -49173,32 +49577,32 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>VIA FERSINA 23</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>TRENTO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -49218,12 +49622,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -49233,7 +49637,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Casella</t>
+          <t>FABBRICO</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -49243,12 +49647,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Castel San Giovanni</t>
+          <t>Fabbrico</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -49262,7 +49666,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>14.49</v>
+        <v>16.806</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -49279,27 +49683,27 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>PIAZZA BORROMEO 14</t>
+          <t>VIA ANTONIO ANDREUZZI 12</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -49319,12 +49723,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -49334,36 +49738,36 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J218" t="n">
-        <v>19.88</v>
+        <v>20</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -49375,32 +49779,32 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA FERSINA 23</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TRENTO</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
@@ -49420,12 +49824,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -49435,36 +49839,36 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Casella</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Castel San Giovanni</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J219" t="n">
-        <v>19.96</v>
+        <v>14.49</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -49481,7 +49885,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>PIAZZA BORROMEO 14</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -49491,7 +49895,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -49521,12 +49925,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -49536,7 +49940,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -49551,7 +49955,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -49565,7 +49969,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>22.925</v>
+        <v>19.88</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -49582,27 +49986,27 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
@@ -49622,12 +50026,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -49637,7 +50041,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -49652,7 +50056,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -49666,7 +50070,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>19.968</v>
+        <v>19.96</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -49683,17 +50087,17 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -49703,7 +50107,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
@@ -49723,12 +50127,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -49738,7 +50142,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -49753,7 +50157,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -49767,7 +50171,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>19.96</v>
+        <v>22.925</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -49784,27 +50188,27 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
@@ -49824,88 +50228,88 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J223" t="n">
-        <v>12</v>
+        <v>19.968</v>
       </c>
       <c r="K223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
@@ -49925,12 +50329,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -49940,36 +50344,36 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J224" t="n">
-        <v>46.7235</v>
+        <v>19.96</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -49986,27 +50390,27 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
@@ -50026,22 +50430,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -50070,34 +50474,34 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -50127,12 +50531,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -50142,7 +50546,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -50157,7 +50561,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -50171,7 +50575,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>18.774</v>
+        <v>46.7235</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -50188,7 +50592,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -50228,22 +50632,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -50253,12 +50657,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -50272,10 +50676,10 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K227" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -50284,32 +50688,32 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
@@ -50329,12 +50733,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -50344,36 +50748,36 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J228" t="n">
-        <v>96.09</v>
+        <v>18.774</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -50390,27 +50794,27 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
@@ -50430,54 +50834,54 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J229" t="n">
-        <v>20.787</v>
+        <v>18</v>
       </c>
       <c r="K229" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -50486,32 +50890,32 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
@@ -50531,12 +50935,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -50546,22 +50950,22 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -50571,11 +50975,11 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J230" t="n">
-        <v>27.867</v>
+        <v>96.09</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -50592,27 +50996,27 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
@@ -50632,12 +51036,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -50647,36 +51051,36 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J231" t="n">
-        <v>28.61</v>
+        <v>20.787</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -50693,27 +51097,27 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>PIAZZA CASTELLO 19</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -50733,12 +51137,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -50748,36 +51152,36 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Prato Smeraldo</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J232" t="n">
-        <v>8.891999999999999</v>
+        <v>27.867</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -50794,40 +51198,343 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
+          <t>VIA BIGLI 2</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PV Cavarzere</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Veneto</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Cavarzere</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>PIAZZA CAVOUR 17</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Latina Fondazione</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>PIAZZA CASTELLO 19</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Prato Smeraldo</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>8.891999999999999</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
           <t>VIALE CASTRENSE 9</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr">
+      <c r="O235" t="inlineStr">
         <is>
           <t>ROMA</t>
         </is>
       </c>
-      <c r="P232" t="inlineStr">
+      <c r="P235" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="Q232" t="inlineStr">
+      <c r="Q235" t="inlineStr">
         <is>
           <t>RM</t>
         </is>
       </c>
-      <c r="R232" t="inlineStr">
+      <c r="R235" t="inlineStr">
         <is>
           <t>Roma Aurelia</t>
         </is>
       </c>
-      <c r="S232" t="inlineStr">
+      <c r="S235" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T232" t="inlineStr">
+      <c r="T235" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U232" t="n">
+      <c r="U235" t="n">
         <v>1</v>
       </c>
     </row>
@@ -50842,7 +51549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53876,12 +54583,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -53891,7 +54598,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PV Cerro Maggiore</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -53901,12 +54608,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Cerro Maggiore</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -53916,11 +54623,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>14.528</v>
+        <v>12.364</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -53937,17 +54644,17 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA LEONE XIII 14</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -53957,7 +54664,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -53977,12 +54684,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -53992,7 +54699,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Scaldasole 41</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -54007,7 +54714,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scaldasole</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -54021,7 +54728,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>37.16</v>
+        <v>14.528</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -54038,17 +54745,17 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -54078,12 +54785,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -54093,7 +54800,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PV Bissina</t>
+          <t>Scaldasole 41</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -54108,7 +54815,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Santa Cristina e Bissone</t>
+          <t>Scaldasole</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -54122,7 +54829,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>78.46299999999999</v>
+        <v>37.16</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -54139,7 +54846,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -54149,7 +54856,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -54179,12 +54886,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -54194,36 +54901,36 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PV Villadose</t>
+          <t>PV Bissina</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Villadose</t>
+          <t>Santa Cristina e Bissone</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>37.481</v>
+        <v>78.46299999999999</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -54240,27 +54947,27 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -54280,12 +54987,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -54295,22 +55002,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GREENFRUT</t>
+          <t>PV Villadose</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bicinicco</t>
+          <t>Villadose</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -54320,11 +55027,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>68.51000000000001</v>
+        <v>37.481</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -54341,27 +55048,27 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>BICINICCO</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -54381,12 +55088,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -54396,36 +55103,36 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>GREENFRUT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Bicinicco</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>18.419</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -54442,40 +55149,141 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
+          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>BICINICCO</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>33050</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>UD</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>STESSA FILIALE</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U36" t="n">
+      <c r="U37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -54490,7 +55298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54691,106 +55499,106 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>310.168</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bergamo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>233.593</v>
+        <v>250</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>220.6</v>
+        <v>233.593</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>193.928</v>
+        <v>220.6</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>160.26</v>
+        <v>193.928</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -55237,40 +56045,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>77.98999999999999</v>
+        <v>80.20400000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>75</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -55279,19 +56087,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -55300,19 +56108,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>71.31999999999999</v>
+        <v>72</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -55321,61 +56129,61 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>71.22999999999999</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>68.51000000000001</v>
+        <v>71.22999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>67.84</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -55594,61 +56402,61 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>51.807</v>
+        <v>53.3</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>51.3</v>
+        <v>51.807</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -55657,19 +56465,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -55678,61 +56486,61 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>50.19</v>
+        <v>50.6</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>47.9</v>
+        <v>50.19</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>47.47</v>
+        <v>47.9</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -55741,28 +56549,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>45.469</v>
+        <v>47.47</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -55771,31 +56579,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>44.036</v>
+        <v>45.469</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>43.65</v>
+        <v>44.036</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -55804,61 +56612,61 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>41.875</v>
+        <v>43.65</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>41.758</v>
+        <v>41.875</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>40.31</v>
+        <v>41.758</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -55867,61 +56675,61 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>39.84</v>
+        <v>40.31</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>37.481</v>
+        <v>39.84</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>36.59</v>
+        <v>37.481</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -55930,19 +56738,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>36.32</v>
+        <v>36.59</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -55951,49 +56759,49 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>35.47</v>
+        <v>36.32</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>34.776</v>
+        <v>35.47</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -56005,7 +56813,7 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>34.6</v>
+        <v>34.776</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -56014,7 +56822,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -56026,7 +56834,7 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>33.972</v>
+        <v>34.6</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -56035,19 +56843,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>33.527</v>
+        <v>33.972</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -56056,28 +56864,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>32.28</v>
+        <v>33.527</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -56086,34 +56894,34 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>31.4</v>
+        <v>32.28</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>30.148</v>
+        <v>31.4</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -56124,35 +56932,35 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>28.61</v>
+        <v>30.148</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>28.38</v>
+        <v>28.61</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -56161,61 +56969,61 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>28.209</v>
+        <v>28.38</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>27.867</v>
+        <v>28.209</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>27.136</v>
+        <v>27.867</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -56224,19 +57032,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>26.95</v>
+        <v>27.136</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -56250,14 +57058,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>25.3</v>
+        <v>26.95</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -56266,19 +57074,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>24.95</v>
+        <v>25.3</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -56287,19 +57095,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>24.94</v>
+        <v>24.95</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -56308,19 +57116,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>24.77</v>
+        <v>24.94</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -56329,19 +57137,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>24</v>
+        <v>24.77</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -56350,19 +57158,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -56371,19 +57179,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>22.925</v>
+        <v>23.2</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -56392,19 +57200,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>22.57</v>
+        <v>22.925</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -56413,19 +57221,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>22</v>
+        <v>22.57</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -56434,12 +57242,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -56449,7 +57257,7 @@
         <v>22</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -56460,77 +57268,77 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>20.787</v>
+        <v>22</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>20</v>
+        <v>20.787</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
         <v>20</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>19.968</v>
+        <v>20</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -56539,7 +57347,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -56551,7 +57359,7 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -56560,19 +57368,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>19.5</v>
+        <v>19.96</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
@@ -56581,19 +57389,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>19.09</v>
+        <v>19.5</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
@@ -56602,19 +57410,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>19.021</v>
+        <v>19.09</v>
       </c>
       <c r="E101" t="n">
         <v>1</v>
@@ -56623,7 +57431,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -56635,7 +57443,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>18.91</v>
+        <v>19.021</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -56644,19 +57452,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>18.419</v>
+        <v>18.91</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -56665,19 +57473,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>18</v>
+        <v>18.419</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -56686,19 +57494,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -56707,19 +57515,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>17.726</v>
+        <v>17.8</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -56728,19 +57536,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>16.806</v>
+        <v>17.726</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
@@ -56749,19 +57557,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>16.63</v>
+        <v>16.806</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -56770,19 +57578,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>16</v>
+        <v>16.63</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -56791,19 +57599,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
@@ -56812,19 +57620,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="E111" t="n">
         <v>1</v>
@@ -56833,19 +57641,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>14.49</v>
+        <v>14.5</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -56854,19 +57662,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>14.03</v>
+        <v>14.49</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -56875,61 +57683,61 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>13.56</v>
+        <v>14</v>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>12.818</v>
+        <v>13.56</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -56938,19 +57746,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>11.7</v>
+        <v>12.818</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -56959,19 +57767,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>11.583</v>
+        <v>11.7</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -56980,19 +57788,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>11.45</v>
+        <v>11.583</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -57001,7 +57809,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -57013,7 +57821,7 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>9.199999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -57022,19 +57830,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>8.984</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -57043,19 +57851,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>8.891999999999999</v>
+        <v>8.984</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -57064,19 +57872,19 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>7.2</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="E123" t="n">
         <v>1</v>
@@ -57085,19 +57893,19 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>7.02</v>
+        <v>7.2</v>
       </c>
       <c r="E124" t="n">
         <v>1</v>
@@ -57106,19 +57914,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="E125" t="n">
         <v>1</v>
@@ -57132,7 +57940,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -57148,19 +57956,19 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E127" t="n">
         <v>1</v>
@@ -57169,43 +57977,43 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -57216,14 +58024,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -57232,19 +58040,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>0.93</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
         <v>1</v>
@@ -57253,19 +58061,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -57279,7 +58087,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -57289,6 +58097,27 @@
         <v>0.5</v>
       </c>
       <c r="E133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Bergamo</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Lucca</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E134" t="n">
         <v>1</v>
       </c>
     </row>
@@ -57325,7 +58154,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
@@ -57335,7 +58164,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11806.8765</v>
+        <v>12022.5485</v>
       </c>
     </row>
     <row r="4">
@@ -57345,7 +58174,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -57355,7 +58184,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -57528,64 +58357,64 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>423.438</v>
+        <v>465.119</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trapani</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>368.48</v>
+        <v>423.438</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Trapani</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>315.211</v>
+        <v>368.48</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -58053,64 +58882,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>96.09</v>
+        <v>102.054</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oristano</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>93.45999999999999</v>
+        <v>96.09</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Oristano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>86.4975</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -58125,94 +58954,94 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>80.658</v>
+        <v>93.02200000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>75.17</v>
+        <v>86.4975</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>73.17</v>
+        <v>75.17</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>72</v>
+        <v>73.17</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Caltanissetta</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>70.23999999999999</v>
+        <v>72</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -58221,82 +59050,82 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Caltanissetta</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>69.26000000000001</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>68.51000000000001</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>67.048</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>64.8</v>
+        <v>67.048</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
@@ -58305,40 +59134,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>63.47500000000001</v>
+        <v>64.8</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>60.95</v>
+        <v>63.47500000000001</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
@@ -58347,22 +59176,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>48.654</v>
+        <v>60.95</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -58744,13 +59573,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C2" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D2" t="n">
-        <v>4639.0595</v>
+        <v>4801.3315</v>
       </c>
     </row>
     <row r="3">
@@ -58760,13 +59589,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>2257.015</v>
+        <v>2310.415</v>
       </c>
     </row>
     <row r="4">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -17005,7 +17005,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -17106,7 +17106,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -18217,7 +18217,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -19025,7 +19025,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -21037,7 +21037,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -21336,7 +21336,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -22144,7 +22144,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -22750,7 +22750,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -23558,7 +23558,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -23962,7 +23962,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -24265,7 +24265,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -24669,7 +24669,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -24972,7 +24972,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -25174,7 +25174,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -25275,7 +25275,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -25477,7 +25477,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -25679,7 +25679,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -26184,7 +26184,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -26689,7 +26689,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -26992,7 +26992,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -27194,7 +27194,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -27295,7 +27295,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -27800,7 +27800,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -27901,7 +27901,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -28204,7 +28204,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -29012,7 +29012,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -29113,7 +29113,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -29214,7 +29214,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -29315,7 +29315,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -29416,7 +29416,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -29618,7 +29618,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -29719,7 +29719,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -29921,7 +29921,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -30123,7 +30123,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -30325,7 +30325,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -30426,7 +30426,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -30527,7 +30527,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -30749,7 +30749,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -30850,7 +30850,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -31254,7 +31254,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -31456,7 +31456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -31557,7 +31557,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -31759,7 +31759,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -31860,7 +31860,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -31961,7 +31961,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -32163,7 +32163,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -32264,7 +32264,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -32365,7 +32365,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -32466,7 +32466,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -32769,7 +32769,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -33072,7 +33072,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -33173,7 +33173,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -33274,7 +33274,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -33375,7 +33375,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -33577,7 +33577,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -33779,7 +33779,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -33880,7 +33880,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -34082,7 +34082,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -34183,7 +34183,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -34284,7 +34284,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -34385,7 +34385,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -34991,7 +34991,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -35092,7 +35092,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -35193,7 +35193,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -35395,7 +35395,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -35496,7 +35496,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -35597,7 +35597,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -35799,7 +35799,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -36102,7 +36102,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -36405,7 +36405,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -36506,7 +36506,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -36708,7 +36708,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -36809,7 +36809,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -36910,7 +36910,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -37112,7 +37112,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -37314,7 +37314,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -37415,7 +37415,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -37516,7 +37516,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -37617,7 +37617,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -37718,7 +37718,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -37819,7 +37819,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -38122,7 +38122,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -38223,7 +38223,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -38324,7 +38324,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -38425,7 +38425,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -38526,7 +38526,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -38627,7 +38627,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -38728,7 +38728,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -38930,7 +38930,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -39031,7 +39031,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -39233,7 +39233,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -39839,7 +39839,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -39940,7 +39940,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -40041,7 +40041,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -40344,7 +40344,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -40445,7 +40445,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -40546,7 +40546,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -40647,7 +40647,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -41051,7 +41051,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -41152,7 +41152,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -41253,7 +41253,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -41354,7 +41354,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -41455,7 +41455,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -41657,7 +41657,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -41859,7 +41859,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -41960,7 +41960,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -42061,7 +42061,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -42162,7 +42162,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -42263,7 +42263,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -42364,7 +42364,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -42465,7 +42465,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -42768,7 +42768,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -42869,7 +42869,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -42970,7 +42970,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -43071,7 +43071,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -43172,7 +43172,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -43374,7 +43374,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -43677,7 +43677,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -43778,7 +43778,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -43879,7 +43879,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -43980,7 +43980,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -44081,7 +44081,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -44283,7 +44283,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -44384,7 +44384,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -44485,7 +44485,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -44687,7 +44687,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -44788,7 +44788,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -44889,7 +44889,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -44990,7 +44990,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -45192,7 +45192,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -45293,7 +45293,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -45495,7 +45495,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -45798,7 +45798,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -45899,7 +45899,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -46000,7 +46000,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -46101,7 +46101,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -46202,7 +46202,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -46404,7 +46404,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -46505,7 +46505,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -46606,7 +46606,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -46707,7 +46707,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -46909,7 +46909,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -47010,7 +47010,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -47111,7 +47111,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -47212,7 +47212,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -47313,7 +47313,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -47414,7 +47414,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -47515,7 +47515,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -47717,7 +47717,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -47818,7 +47818,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -47919,7 +47919,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -48020,7 +48020,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -48121,7 +48121,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -48323,7 +48323,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -48424,7 +48424,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -48626,7 +48626,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -48727,7 +48727,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -48828,7 +48828,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -49026,7 +49026,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -49127,7 +49127,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -49430,7 +49430,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -49531,7 +49531,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -49733,7 +49733,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -49834,7 +49834,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -49935,7 +49935,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -50036,7 +50036,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -50137,7 +50137,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -50238,7 +50238,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -50339,7 +50339,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -50440,7 +50440,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -50541,7 +50541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -50642,7 +50642,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -50743,7 +50743,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -50844,7 +50844,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -50945,7 +50945,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -51046,7 +51046,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -51248,7 +51248,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -51349,7 +51349,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -51450,7 +51450,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -51551,7 +51551,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -51652,7 +51652,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -51753,7 +51753,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -51955,7 +51955,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -52056,7 +52056,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -52157,7 +52157,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -52258,7 +52258,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -52359,7 +52359,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -52460,7 +52460,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -52561,7 +52561,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -52662,7 +52662,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -52763,7 +52763,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -52864,7 +52864,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -52965,7 +52965,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -53066,7 +53066,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -53369,7 +53369,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -53470,7 +53470,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -53571,7 +53571,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -53672,7 +53672,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -53874,7 +53874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -53975,7 +53975,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -54379,7 +54379,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -54480,7 +54480,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -54682,7 +54682,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -54783,7 +54783,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -55086,7 +55086,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -55288,7 +55288,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -55389,7 +55389,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -55490,7 +55490,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -55591,7 +55591,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -55692,7 +55692,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -55793,7 +55793,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -55894,7 +55894,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -55995,7 +55995,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -56096,7 +56096,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -56197,7 +56197,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -56298,7 +56298,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -56500,7 +56500,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -56601,7 +56601,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -56702,7 +56702,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -56803,7 +56803,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -57025,7 +57025,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -57126,7 +57126,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -57227,7 +57227,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -57328,7 +57328,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -57530,7 +57530,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -57631,7 +57631,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -58136,7 +58136,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -58439,7 +58439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -58540,7 +58540,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -58641,7 +58641,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -58742,7 +58742,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -58944,7 +58944,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -59045,7 +59045,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -59146,7 +59146,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -59247,7 +59247,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -59344,7 +59344,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -59441,7 +59441,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -59542,7 +59542,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -59643,7 +59643,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -59744,7 +59744,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -59845,7 +59845,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -59946,7 +59946,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -60047,7 +60047,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -60148,7 +60148,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -60249,7 +60249,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -60855,7 +60855,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U300"/>
+  <dimension ref="A1:U301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25770,12 +25770,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -25785,7 +25785,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Ospedaletto Lodigiano</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -25795,12 +25795,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Lodi</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Ospedaletto Lodigiano</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -25810,11 +25810,11 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="J252" t="n">
-        <v>7.2</v>
+        <v>19.191</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -25871,12 +25871,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Solaro</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -25896,12 +25896,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Solaro</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -25915,7 +25915,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>12.818</v>
+        <v>7.2</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>VIALE DON LUIGI STURZO 43</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -25942,7 +25942,7 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
@@ -25952,12 +25952,12 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
@@ -25972,12 +25972,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -25987,7 +25987,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>Solaro</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -26002,7 +26002,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Solaro</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -26012,11 +26012,11 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J254" t="n">
-        <v>67.84</v>
+        <v>12.818</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -26033,7 +26033,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIALE DON LUIGI STURZO 43</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
@@ -26053,7 +26053,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
@@ -26073,12 +26073,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -26088,7 +26088,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>PV Cerro Maggiore</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -26103,7 +26103,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Cerro Maggiore</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -26117,7 +26117,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>12.364</v>
+        <v>67.84</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -26134,7 +26134,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>VIA LEONE XIII 14</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
@@ -26174,12 +26174,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -26189,7 +26189,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Cerro Maggiore</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -26199,12 +26199,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Cerro Maggiore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -26214,11 +26214,11 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J256" t="n">
-        <v>40.31</v>
+        <v>12.364</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -26235,32 +26235,32 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA LEONE XIII 14</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
@@ -26275,12 +26275,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>14.528</v>
+        <v>40.31</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -26336,32 +26336,32 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
@@ -26376,22 +26376,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Scaldasole 41</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Scaldasole</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -26420,7 +26420,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>37.16</v>
+        <v>14.528</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -26437,17 +26437,17 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -26477,12 +26477,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -26492,22 +26492,22 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>PV Alessandria</t>
+          <t>Scaldasole 41</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Scaldasole</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -26521,7 +26521,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>5</v>
+        <v>37.16</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -26533,37 +26533,37 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
@@ -26593,7 +26593,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>PV Tortona</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Tortona</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -26622,7 +26622,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -26679,12 +26679,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -26694,22 +26694,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>PV Bissina</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Santa Cristina e Bissone</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -26723,7 +26723,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>78.46299999999999</v>
+        <v>10</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -26740,32 +26740,32 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
@@ -26780,22 +26780,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Cascina Grande</t>
+          <t>PV Bissina</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -26810,7 +26810,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Dorno</t>
+          <t>Santa Cristina e Bissone</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -26824,7 +26824,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>121.697</v>
+        <v>78.46299999999999</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -26841,32 +26841,32 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>VIA GIOSUE' CARDUCCI 8</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
@@ -26881,12 +26881,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -26896,22 +26896,22 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Spinetta Marengo PV</t>
+          <t>Cascina Grande</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Dorno</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>11.8</v>
+        <v>121.697</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -26942,27 +26942,27 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>VIALE REGINA MARGHERITA, 125</t>
+          <t>VIA GIOSUE' CARDUCCI 8</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TRIESTE</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
@@ -26982,12 +26982,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -26997,36 +26997,36 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Spinetta Marengo PV</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J264" t="n">
-        <v>48.5</v>
+        <v>11.8</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -27043,27 +27043,27 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIALE REGINA MARGHERITA, 125</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
@@ -27098,7 +27098,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -27108,12 +27108,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -27127,7 +27127,7 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -27184,22 +27184,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -27228,7 +27228,7 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -27245,17 +27245,17 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
@@ -27265,7 +27265,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
@@ -27285,22 +27285,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -27329,7 +27329,7 @@
         </is>
       </c>
       <c r="J267" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -27346,27 +27346,27 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
@@ -27386,12 +27386,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -27401,7 +27401,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -27430,7 +27430,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>29.73</v>
+        <v>36.32</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -27447,27 +27447,27 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
@@ -27487,22 +27487,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>PV Villadose</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Villadose</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>37.481</v>
+        <v>29.73</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -27548,32 +27548,32 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T269" t="inlineStr">
@@ -27588,12 +27588,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -27603,7 +27603,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>CASTELNOVO B.</t>
+          <t>PV Villadose</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -27618,7 +27618,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Castelnovo Bariano</t>
+          <t>Villadose</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -27632,7 +27632,7 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>15.03</v>
+        <v>37.481</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -27649,32 +27649,32 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>VIA VARESE 194</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T270" t="inlineStr">
@@ -27689,12 +27689,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Bagnoli 1, 2, 3, 4</t>
+          <t>CASTELNOVO B.</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -27714,26 +27714,26 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
+          <t>Rovigo</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Castelnovo Bariano</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
           <t>Padova</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>Bagnoli di Sopra</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>Padova</t>
-        </is>
-      </c>
       <c r="J271" t="n">
-        <v>26.67</v>
+        <v>15.03</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -27750,7 +27750,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>VIA VARESE 194</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -27760,7 +27760,7 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
@@ -27770,7 +27770,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S271" t="inlineStr">
@@ -27790,12 +27790,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>PV via Murazze snc</t>
+          <t>Bagnoli 1, 2, 3, 4</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -27815,12 +27815,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Porto Viro</t>
+          <t>Bagnoli di Sopra</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -27834,7 +27834,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>19.56</v>
+        <v>26.67</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -27891,22 +27891,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>PV Ariano nel Polese</t>
+          <t>PV via Murazze snc</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -27921,7 +27921,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Ariano nel Polesine</t>
+          <t>Porto Viro</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>19.09</v>
+        <v>19.56</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -27952,7 +27952,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>VIA GIANFRANCO MALIPIERO 16-18</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
@@ -27992,12 +27992,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>PV Stienta</t>
+          <t>PV Ariano nel Polese</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Stienta</t>
+          <t>Ariano nel Polesine</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -28036,7 +28036,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>117.9</v>
+        <v>19.09</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -28053,7 +28053,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>VIA FELICE CAVALLOTTI 13</t>
+          <t>VIA GIANFRANCO MALIPIERO 16-18</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -28063,7 +28063,7 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
@@ -28073,7 +28073,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
@@ -28093,22 +28093,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>PV Guarda Veneta</t>
+          <t>PV Stienta</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Guarda Veneta</t>
+          <t>Stienta</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -28137,7 +28137,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>32.008</v>
+        <v>117.9</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -28154,7 +28154,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>PIAZZALE LUIGI CADORNA 6</t>
+          <t>VIA FELICE CAVALLOTTI 13</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
@@ -28194,12 +28194,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>PV Costa di Rovigo</t>
+          <t>PV Guarda Veneta</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Costa di Rovigo</t>
+          <t>Guarda Veneta</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -28238,7 +28238,7 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>58.917</v>
+        <v>32.008</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -28255,32 +28255,32 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+          <t>PIAZZALE LUIGI CADORNA 6</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T276" t="inlineStr">
@@ -28295,93 +28295,93 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV Costa di Rovigo</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Costa di Rovigo</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J277" t="n">
-        <v>7</v>
+        <v>58.917</v>
       </c>
       <c r="K277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T277" t="inlineStr">
@@ -28396,12 +28396,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -28421,63 +28421,63 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J278" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -28497,22 +28497,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>FABBRICO</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -28522,12 +28522,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Fabbrico</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -28541,7 +28541,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>16.806</v>
+        <v>72</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -28558,27 +28558,27 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>VIA ANTONIO ANDREUZZI 12</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -28598,12 +28598,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>FABBRICO</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -28628,7 +28628,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>Fabbrico</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -28642,7 +28642,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>20</v>
+        <v>16.806</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -28654,32 +28654,32 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>VIA FERSINA 23</t>
+          <t>VIA ANTONIO ANDREUZZI 12</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>TRENTO</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
@@ -28699,22 +28699,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Casella</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -28724,12 +28724,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Castel San Giovanni</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -28743,7 +28743,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>14.49</v>
+        <v>20</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -28755,32 +28755,32 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>PIAZZA BORROMEO 14</t>
+          <t>VIA FERSINA 23</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TRENTO</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -28800,51 +28800,51 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Casella</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Castel San Giovanni</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J282" t="n">
-        <v>19.88</v>
+        <v>14.49</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -28861,27 +28861,27 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>PIAZZA BORROMEO 14</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
@@ -28901,22 +28901,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -28945,7 +28945,7 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -28962,27 +28962,27 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
@@ -29002,12 +29002,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -29017,7 +29017,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -29032,7 +29032,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -29046,7 +29046,7 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -29063,27 +29063,27 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
@@ -29103,12 +29103,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -29133,7 +29133,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -29147,7 +29147,7 @@
         </is>
       </c>
       <c r="J285" t="n">
-        <v>19.968</v>
+        <v>22.925</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -29164,27 +29164,27 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -29204,12 +29204,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -29234,7 +29234,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -29248,7 +29248,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -29265,27 +29265,27 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
@@ -29305,12 +29305,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -29320,73 +29320,73 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
@@ -29406,12 +29406,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -29450,44 +29450,44 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
@@ -29507,12 +29507,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -29537,7 +29537,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -29551,7 +29551,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -29568,27 +29568,27 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -29608,12 +29608,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -29623,7 +29623,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -29638,7 +29638,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -29669,27 +29669,27 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
@@ -29709,12 +29709,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -29724,7 +29724,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -29734,12 +29734,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -29753,10 +29753,10 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K291" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -29765,32 +29765,32 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
@@ -29810,12 +29810,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -29825,39 +29825,39 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J292" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K292" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -29866,32 +29866,32 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
@@ -29911,22 +29911,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>GREENFRUT</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -29936,26 +29936,26 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
+          <t>Pordenone</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Maniago</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
           <t>Udine</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>Bicinicco</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>Udine</t>
-        </is>
-      </c>
       <c r="J293" t="n">
-        <v>68.51000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -29972,32 +29972,32 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>BICINICCO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
@@ -30012,37 +30012,37 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>GREENFRUT</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Bicinicco</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -30052,11 +30052,11 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J294" t="n">
-        <v>20.787</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -30073,32 +30073,32 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BICINICCO</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>33050</t>
         </is>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -30113,22 +30113,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -30143,7 +30143,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -30157,7 +30157,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>27.867</v>
+        <v>20.787</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -30174,27 +30174,27 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
@@ -30214,22 +30214,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>PV Cavarzere</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Cavarzere</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -30258,7 +30258,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>53.4</v>
+        <v>27.867</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -30275,27 +30275,27 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>PIAZZA CAVOUR 17</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -30315,12 +30315,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -30330,36 +30330,36 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV Cavarzere</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Cavarzere</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J297" t="n">
-        <v>18.419</v>
+        <v>53.4</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -30376,32 +30376,32 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>VIA ALDO MORO 233</t>
+          <t>PIAZZA CAVOUR 17</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>FROSINONE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T297" t="inlineStr">
@@ -30416,12 +30416,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -30431,7 +30431,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>EGPM-FV082</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -30446,7 +30446,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pontinia</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -30460,7 +30460,7 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>28.61</v>
+        <v>18.419</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -30477,32 +30477,32 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>PIAZZA CASTELLO 19</t>
+          <t>VIA ALDO MORO 233</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FROSINONE</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
@@ -30517,12 +30517,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Prato Smeraldo</t>
+          <t>Latina Fondazione</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -30547,7 +30547,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -30561,7 +30561,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>8.891999999999999</v>
+        <v>28.61</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -30578,27 +30578,27 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>VIALE CASTRENSE 9</t>
+          <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
@@ -30618,12 +30618,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -30633,7 +30633,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>PV Paliano</t>
+          <t>Prato Smeraldo</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -30643,26 +30643,26 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Paliano</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
       <c r="J300" t="n">
-        <v>38.99</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -30679,40 +30679,141 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
+          <t>VIALE CASTRENSE 9</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>PV Paliano</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Paliano</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J301" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
           <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
-      <c r="O300" t="inlineStr">
+      <c r="O301" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P300" t="inlineStr">
+      <c r="P301" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q300" t="inlineStr">
+      <c r="Q301" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R300" t="inlineStr">
+      <c r="R301" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S300" t="inlineStr">
+      <c r="S301" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T300" t="inlineStr">
+      <c r="T301" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U300" t="n">
+      <c r="U301" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30727,7 +30828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U261"/>
+  <dimension ref="A1:U262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53157,12 +53258,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -53172,7 +53273,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Ospedaletto Lodigiano</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -53182,12 +53283,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Lodi</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Ospedaletto Lodigiano</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -53197,11 +53298,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="J223" t="n">
-        <v>7.2</v>
+        <v>19.191</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -53258,12 +53359,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -53273,7 +53374,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -53283,12 +53384,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -53298,11 +53399,11 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J224" t="n">
-        <v>40.31</v>
+        <v>7.2</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -53319,27 +53420,27 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
@@ -53359,37 +53460,37 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>PV Alessandria</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -53403,7 +53504,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>5</v>
+        <v>40.31</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -53415,32 +53516,32 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
@@ -53475,7 +53576,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>PV Tortona</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -53490,7 +53591,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tortona</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -53504,7 +53605,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -53516,7 +53617,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -53561,37 +53662,37 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Cascina Grande</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dorno</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -53605,7 +53706,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>121.697</v>
+        <v>10</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -53622,27 +53723,27 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>VIA GIOSUE' CARDUCCI 8</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
@@ -53662,12 +53763,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -53677,22 +53778,22 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Spinetta Marengo PV</t>
+          <t>Cascina Grande</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Dorno</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -53706,7 +53807,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>11.8</v>
+        <v>121.697</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -53723,27 +53824,27 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>VIALE REGINA MARGHERITA, 125</t>
+          <t>VIA GIOSUE' CARDUCCI 8</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TRIESTE</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
@@ -53763,12 +53864,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -53778,36 +53879,36 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Spinetta Marengo PV</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J229" t="n">
-        <v>48.5</v>
+        <v>11.8</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -53824,27 +53925,27 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIALE REGINA MARGHERITA, 125</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
@@ -53879,7 +53980,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -53889,12 +53990,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -53908,7 +54009,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -53965,22 +54066,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -53995,7 +54096,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -54009,7 +54110,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -54026,17 +54127,17 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -54046,7 +54147,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -54066,22 +54167,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -54096,7 +54197,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -54110,7 +54211,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -54127,27 +54228,27 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
@@ -54167,12 +54268,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -54182,7 +54283,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -54197,7 +54298,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -54211,7 +54312,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>29.73</v>
+        <v>36.32</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -54228,27 +54329,27 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
@@ -54268,22 +54369,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>CASTELNOVO B.</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -54298,7 +54399,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Castelnovo Bariano</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -54312,7 +54413,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>15.03</v>
+        <v>29.73</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -54329,7 +54430,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>VIA VARESE 194</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -54339,7 +54440,7 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -54349,7 +54450,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
@@ -54369,12 +54470,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -54384,7 +54485,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Bagnoli 1, 2, 3, 4</t>
+          <t>CASTELNOVO B.</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -54394,26 +54495,26 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
+          <t>Rovigo</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Castelnovo Bariano</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
           <t>Padova</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Bagnoli di Sopra</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>Padova</t>
-        </is>
-      </c>
       <c r="J235" t="n">
-        <v>26.67</v>
+        <v>15.03</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -54430,7 +54531,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>VIA VARESE 194</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -54440,7 +54541,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
@@ -54450,7 +54551,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -54470,12 +54571,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -54485,7 +54586,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>PV via Murazze snc</t>
+          <t>Bagnoli 1, 2, 3, 4</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -54495,12 +54596,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Porto Viro</t>
+          <t>Bagnoli di Sopra</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -54514,7 +54615,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>19.56</v>
+        <v>26.67</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -54571,22 +54672,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>PV Ariano nel Polese</t>
+          <t>PV via Murazze snc</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -54601,7 +54702,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Ariano nel Polesine</t>
+          <t>Porto Viro</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -54615,7 +54716,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>19.09</v>
+        <v>19.56</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -54632,7 +54733,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>VIA GIANFRANCO MALIPIERO 16-18</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -54642,7 +54743,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -54652,7 +54753,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
@@ -54672,12 +54773,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -54687,7 +54788,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>PV Stienta</t>
+          <t>PV Ariano nel Polese</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -54702,7 +54803,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Stienta</t>
+          <t>Ariano nel Polesine</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -54716,7 +54817,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>117.9</v>
+        <v>19.09</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -54733,7 +54834,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>VIA FELICE CAVALLOTTI 13</t>
+          <t>VIA GIANFRANCO MALIPIERO 16-18</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -54743,7 +54844,7 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
@@ -54753,7 +54854,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -54773,22 +54874,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>PV Guarda Veneta</t>
+          <t>PV Stienta</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -54803,7 +54904,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Guarda Veneta</t>
+          <t>Stienta</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -54817,7 +54918,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>32.008</v>
+        <v>117.9</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -54834,7 +54935,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>PIAZZALE LUIGI CADORNA 6</t>
+          <t>VIA FELICE CAVALLOTTI 13</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -54844,7 +54945,7 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -54874,88 +54975,88 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>PV Guarda Veneta</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Guarda Veneta</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J240" t="n">
-        <v>7</v>
+        <v>32.008</v>
       </c>
       <c r="K240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>PIAZZALE LUIGI CADORNA 6</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
@@ -54975,12 +55076,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -54990,7 +55091,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -55000,63 +55101,63 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J241" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
@@ -55076,22 +55177,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>FABBRICO</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -55101,12 +55202,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fabbrico</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -55120,7 +55221,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>16.806</v>
+        <v>72</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -55137,27 +55238,27 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>VIA ANTONIO ANDREUZZI 12</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
@@ -55177,12 +55278,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -55192,7 +55293,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>FABBRICO</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -55207,7 +55308,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>Fabbrico</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -55221,7 +55322,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>20</v>
+        <v>16.806</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -55233,32 +55334,32 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>VIA FERSINA 23</t>
+          <t>VIA ANTONIO ANDREUZZI 12</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>TRENTO</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
@@ -55278,22 +55379,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Casella</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -55303,12 +55404,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Castel San Giovanni</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -55322,7 +55423,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>14.49</v>
+        <v>20</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -55334,32 +55435,32 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>PIAZZA BORROMEO 14</t>
+          <t>VIA FERSINA 23</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TRENTO</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
@@ -55379,51 +55480,51 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Casella</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Piacenza</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Castel San Giovanni</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J245" t="n">
-        <v>19.88</v>
+        <v>14.49</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -55440,27 +55541,27 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>PIAZZA BORROMEO 14</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -55480,22 +55581,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -55524,7 +55625,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -55541,27 +55642,27 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
@@ -55581,12 +55682,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -55596,7 +55697,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -55611,7 +55712,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -55625,7 +55726,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -55642,27 +55743,27 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
@@ -55682,12 +55783,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -55697,7 +55798,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -55712,7 +55813,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -55726,7 +55827,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>19.968</v>
+        <v>22.925</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -55743,27 +55844,27 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
@@ -55783,12 +55884,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -55798,7 +55899,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -55813,7 +55914,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -55827,7 +55928,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -55844,27 +55945,27 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
@@ -55884,12 +55985,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -55899,73 +56000,73 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J250" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
@@ -55985,12 +56086,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -56000,7 +56101,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -56015,7 +56116,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -56029,44 +56130,44 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -56086,12 +56187,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -56101,7 +56202,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -56116,7 +56217,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -56130,7 +56231,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -56147,27 +56248,27 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -56187,12 +56288,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -56202,7 +56303,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -56217,7 +56318,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -56231,7 +56332,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -56248,27 +56349,27 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
@@ -56288,12 +56389,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -56303,7 +56404,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -56313,12 +56414,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -56332,10 +56433,10 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K254" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -56344,32 +56445,32 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
@@ -56389,12 +56490,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -56404,39 +56505,39 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J255" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K255" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -56445,32 +56546,32 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -56490,12 +56591,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -56505,22 +56606,22 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Maniago</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -56530,11 +56631,11 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J256" t="n">
-        <v>20.787</v>
+        <v>96.09</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -56551,27 +56652,27 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
@@ -56591,22 +56692,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -56621,7 +56722,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -56635,7 +56736,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>27.867</v>
+        <v>20.787</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -56652,27 +56753,27 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
@@ -56692,22 +56793,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>PV Cavarzere</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -56722,7 +56823,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Cavarzere</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -56736,7 +56837,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>53.4</v>
+        <v>27.867</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -56753,27 +56854,27 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>PIAZZA CAVOUR 17</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
@@ -56793,12 +56894,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -56808,36 +56909,36 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>PV Cavarzere</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Cavarzere</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J259" t="n">
-        <v>28.61</v>
+        <v>53.4</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -56854,27 +56955,27 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>PIAZZA CASTELLO 19</t>
+          <t>PIAZZA CAVOUR 17</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
@@ -56894,12 +56995,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -56909,7 +57010,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Prato Smeraldo</t>
+          <t>Latina Fondazione</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -56924,7 +57025,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -56938,7 +57039,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>8.891999999999999</v>
+        <v>28.61</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -56955,27 +57056,27 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>VIALE CASTRENSE 9</t>
+          <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
@@ -56995,12 +57096,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -57010,7 +57111,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>PV Paliano</t>
+          <t>Prato Smeraldo</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -57020,26 +57121,26 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Paliano</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
       <c r="J261" t="n">
-        <v>38.99</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -57056,40 +57157,141 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
+          <t>VIALE CASTRENSE 9</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>PV Paliano</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Paliano</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
           <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
-      <c r="O261" t="inlineStr">
+      <c r="O262" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P261" t="inlineStr">
+      <c r="P262" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q261" t="inlineStr">
+      <c r="Q262" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R261" t="inlineStr">
+      <c r="R262" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S261" t="inlineStr">
+      <c r="S262" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T261" t="inlineStr">
+      <c r="T262" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U261" t="n">
+      <c r="U262" t="n">
         <v>1</v>
       </c>
     </row>
@@ -61156,7 +61358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63310,19 +63512,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>Milano Est</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Padova</t>
-        </is>
-      </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>19.09</v>
+        <v>19.191</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -63331,19 +63533,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>19.021</v>
+        <v>19.09</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -63352,7 +63554,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -63364,7 +63566,7 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>18.91</v>
+        <v>19.021</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -63373,19 +63575,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>18.419</v>
+        <v>18.91</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -63394,19 +63596,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>18</v>
+        <v>18.419</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
@@ -63415,19 +63617,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>17.726</v>
+        <v>18</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -63436,19 +63638,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>16.806</v>
+        <v>17.726</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -63457,19 +63659,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>16.63</v>
+        <v>16.806</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
@@ -63478,19 +63680,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>16</v>
+        <v>16.63</v>
       </c>
       <c r="E111" t="n">
         <v>1</v>
@@ -63499,61 +63701,61 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>15.721</v>
+        <v>16</v>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>15</v>
+        <v>15.721</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -63562,19 +63764,19 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>14.49</v>
+        <v>14.5</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -63583,19 +63785,19 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>14.03</v>
+        <v>14.49</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -63604,61 +63806,61 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>13.887</v>
+        <v>14</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>13.686</v>
+        <v>13.887</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -63667,19 +63869,19 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>13.56</v>
+        <v>13.686</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -63688,19 +63890,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>12.818</v>
+        <v>13.56</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -63709,19 +63911,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>12.818</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -63735,14 +63937,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>11.583</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="n">
         <v>1</v>
@@ -63751,19 +63953,19 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>11.45</v>
+        <v>11.583</v>
       </c>
       <c r="E124" t="n">
         <v>1</v>
@@ -63772,19 +63974,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>9.388</v>
+        <v>11.45</v>
       </c>
       <c r="E125" t="n">
         <v>1</v>
@@ -63793,19 +63995,19 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>9.199999999999999</v>
+        <v>9.388</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
@@ -63814,19 +64016,19 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>8.891999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E127" t="n">
         <v>1</v>
@@ -63835,19 +64037,19 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>7.2</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
@@ -63856,19 +64058,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
@@ -63882,7 +64084,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -63898,19 +64100,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="E131" t="n">
         <v>1</v>
@@ -63919,19 +64121,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>6.7</v>
+        <v>6.86</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -63945,14 +64147,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>6.562</v>
+        <v>6.7</v>
       </c>
       <c r="E133" t="n">
         <v>1</v>
@@ -63961,49 +64163,49 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>5.4</v>
+        <v>6.562</v>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -64015,7 +64217,7 @@
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -64024,19 +64226,19 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="E137" t="n">
         <v>1</v>
@@ -64045,63 +64247,84 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
         <v>2</v>
       </c>
-      <c r="D138" t="n">
-        <v>1.32</v>
-      </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bergamo</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>0.93</v>
+        <v>1.32</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>Bergamo</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Lucca</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" t="n">
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
         <v>0.5</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -64138,7 +64361,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -64148,7 +64371,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12807.9175</v>
+        <v>12827.1085</v>
       </c>
     </row>
     <row r="4">
@@ -64168,7 +64391,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -64182,7 +64405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65433,19 +65656,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lodi</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>18.91</v>
+        <v>19.191</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -65454,19 +65677,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>18</v>
+        <v>18.91</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -65475,19 +65698,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>17.169</v>
+        <v>18</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -65496,19 +65719,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>9.196</v>
+        <v>17.169</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -65517,7 +65740,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -65526,33 +65749,54 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>7.2</v>
+        <v>9.196</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>7.2</v>
       </c>
       <c r="E65" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Monza e della Brianza</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Lombardia</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -65599,13 +65843,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D2" t="n">
-        <v>5122.4575</v>
+        <v>5141.6485</v>
       </c>
     </row>
     <row r="3">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U315"/>
+  <dimension ref="A1:U316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31527,12 +31527,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -31542,22 +31542,22 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>PV Sesto al Reghena</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Sesto al Reghena</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -31567,11 +31567,11 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>20.787</v>
+        <v>55.94</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -31588,27 +31588,27 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA CARAVAGGIO 125</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
@@ -31628,12 +31628,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -31643,7 +31643,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -31672,7 +31672,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>27.867</v>
+        <v>20.787</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -31689,27 +31689,27 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
@@ -31729,12 +31729,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -31744,7 +31744,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>PV Cavarzere</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -31759,7 +31759,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Cavarzere</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -31773,7 +31773,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>53.4</v>
+        <v>27.867</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -31790,27 +31790,27 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>PIAZZA CAVOUR 17</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
@@ -31830,12 +31830,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -31845,36 +31845,36 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV Cavarzere</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Cavarzere</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>18.419</v>
+        <v>53.4</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -31891,32 +31891,32 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>VIA ALDO MORO 233</t>
+          <t>PIAZZA CAVOUR 17</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>FROSINONE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T312" t="inlineStr">
@@ -31931,12 +31931,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -31946,7 +31946,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>EGPM-FV082</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -31961,7 +31961,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pontinia</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -31975,7 +31975,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>28.61</v>
+        <v>18.419</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -31992,32 +31992,32 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>PIAZZA CASTELLO 19</t>
+          <t>VIA ALDO MORO 233</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FROSINONE</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T313" t="inlineStr">
@@ -32032,12 +32032,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -32047,7 +32047,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Prato Smeraldo</t>
+          <t>Latina Fondazione</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -32076,7 +32076,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>8.891999999999999</v>
+        <v>28.61</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -32093,27 +32093,27 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>VIALE CASTRENSE 9</t>
+          <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S314" t="inlineStr">
@@ -32133,12 +32133,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>PV Paliano</t>
+          <t>Prato Smeraldo</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -32158,26 +32158,26 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>Paliano</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
       <c r="J315" t="n">
-        <v>38.99</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -32194,40 +32194,141 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
+          <t>VIALE CASTRENSE 9</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>PV Paliano</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Paliano</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
           <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
-      <c r="O315" t="inlineStr">
+      <c r="O316" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P315" t="inlineStr">
+      <c r="P316" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q315" t="inlineStr">
+      <c r="Q316" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R315" t="inlineStr">
+      <c r="R316" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S315" t="inlineStr">
+      <c r="S316" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T315" t="inlineStr">
+      <c r="T316" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U315" t="n">
+      <c r="U316" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32242,7 +32343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U276"/>
+  <dimension ref="A1:U277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59520,12 +59621,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -59535,22 +59636,22 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>PV Sesto al Reghena</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Sesto al Reghena</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -59560,11 +59661,11 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J271" t="n">
-        <v>20.787</v>
+        <v>55.94</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -59581,27 +59682,27 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA CARAVAGGIO 125</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S271" t="inlineStr">
@@ -59621,12 +59722,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -59636,7 +59737,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -59651,7 +59752,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -59665,7 +59766,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>27.867</v>
+        <v>20.787</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -59682,27 +59783,27 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
@@ -59722,12 +59823,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -59737,7 +59838,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>PV Cavarzere</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -59752,7 +59853,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Cavarzere</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -59766,7 +59867,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>53.4</v>
+        <v>27.867</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -59783,27 +59884,27 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>PIAZZA CAVOUR 17</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
@@ -59823,12 +59924,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -59838,36 +59939,36 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>PV Cavarzere</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Cavarzere</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J274" t="n">
-        <v>28.61</v>
+        <v>53.4</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -59884,27 +59985,27 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>PIAZZA CASTELLO 19</t>
+          <t>PIAZZA CAVOUR 17</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
@@ -59924,12 +60025,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -59939,7 +60040,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Prato Smeraldo</t>
+          <t>Latina Fondazione</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -59954,7 +60055,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -59968,7 +60069,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>8.891999999999999</v>
+        <v>28.61</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -59985,27 +60086,27 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>VIALE CASTRENSE 9</t>
+          <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
@@ -60025,12 +60126,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -60040,7 +60141,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>PV Paliano</t>
+          <t>Prato Smeraldo</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -60050,26 +60151,26 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>Paliano</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
       <c r="J276" t="n">
-        <v>38.99</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -60086,40 +60187,141 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
+          <t>VIALE CASTRENSE 9</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>PV Paliano</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Paliano</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
           <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
-      <c r="O276" t="inlineStr">
+      <c r="O277" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P276" t="inlineStr">
+      <c r="P277" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q276" t="inlineStr">
+      <c r="Q277" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R276" t="inlineStr">
+      <c r="R277" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S276" t="inlineStr">
+      <c r="S277" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T276" t="inlineStr">
+      <c r="T277" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U276" t="n">
+      <c r="U277" t="n">
         <v>1</v>
       </c>
     </row>
@@ -64186,7 +64388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65374,19 +65576,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>55.55</v>
+        <v>55.94</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -65395,103 +65597,103 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>55.09999999999999</v>
+        <v>55.55</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>53.4</v>
+        <v>55.09999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>51.807</v>
+        <v>53.3</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>51.3</v>
+        <v>51.807</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -65500,7 +65702,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -65509,61 +65711,61 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>50.19</v>
+        <v>51.3</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>47.9</v>
+        <v>50.19</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>45.469</v>
+        <v>47.9</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -65572,31 +65774,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>44.036</v>
+        <v>45.469</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>43.65</v>
+        <v>44.036</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -65605,64 +65807,64 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>41.875</v>
+        <v>43.65</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>41.758</v>
+        <v>41.875</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>40.73999999999999</v>
+        <v>41.758</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -65673,77 +65875,77 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>40.31</v>
+        <v>40.73999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>39.84</v>
+        <v>40.31</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>36.59</v>
+        <v>39.84</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>36.32</v>
+        <v>36.59</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -65752,49 +65954,49 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>35.47</v>
+        <v>36.32</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>34.776</v>
+        <v>35.47</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -65806,7 +66008,7 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>34.6</v>
+        <v>34.776</v>
       </c>
       <c r="E77" t="n">
         <v>1</v>
@@ -65815,7 +66017,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -65827,7 +66029,7 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>33.972</v>
+        <v>34.6</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
@@ -65836,19 +66038,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>33.527</v>
+        <v>33.972</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -65857,28 +66059,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>32.28</v>
+        <v>33.527</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -65887,115 +66089,115 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>31.4</v>
+        <v>32.28</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>30.148</v>
+        <v>31.4</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>28.38</v>
+        <v>30.148</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>28.209</v>
+        <v>28.38</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>27.867</v>
+        <v>28.209</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>27.136</v>
+        <v>27.867</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -66004,19 +66206,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>25.3</v>
+        <v>27.136</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -66025,19 +66227,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>24.95</v>
+        <v>25.3</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -66046,19 +66248,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>24.94</v>
+        <v>24.95</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -66067,19 +66269,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>24.77</v>
+        <v>24.94</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -66088,19 +66290,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>24</v>
+        <v>24.77</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -66109,19 +66311,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -66130,19 +66332,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>22.925</v>
+        <v>23.2</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -66151,19 +66353,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>22.57</v>
+        <v>22.925</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -66172,19 +66374,19 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>22</v>
+        <v>22.57</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -66193,12 +66395,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -66208,7 +66410,7 @@
         <v>22</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -66219,77 +66421,77 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>20.787</v>
+        <v>22</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>20</v>
+        <v>20.787</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>20</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>19.968</v>
+        <v>20</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
@@ -66298,7 +66500,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -66310,7 +66512,7 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="E101" t="n">
         <v>1</v>
@@ -66319,19 +66521,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>19.5</v>
+        <v>19.96</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -66340,19 +66542,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>19.191</v>
+        <v>19.5</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -66361,19 +66563,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>Milano Est</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Padova</t>
-        </is>
-      </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>19.09</v>
+        <v>19.191</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -66382,19 +66584,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>19.021</v>
+        <v>19.09</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -66403,7 +66605,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -66415,7 +66617,7 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>18.91</v>
+        <v>19.021</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -66424,19 +66626,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>18.419</v>
+        <v>18.91</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
@@ -66445,19 +66647,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>18</v>
+        <v>18.419</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -66466,19 +66668,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>17.726</v>
+        <v>18</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -66487,19 +66689,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>16.806</v>
+        <v>17.726</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
@@ -66508,19 +66710,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>16.63</v>
+        <v>16.806</v>
       </c>
       <c r="E111" t="n">
         <v>1</v>
@@ -66529,19 +66731,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sassari</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>16</v>
+        <v>16.63</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -66550,61 +66752,61 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sassari</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>15.721</v>
+        <v>16</v>
       </c>
       <c r="E113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>15.336</v>
+        <v>15.721</v>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>15</v>
+        <v>15.336</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -66613,19 +66815,19 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -66634,19 +66836,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>14.49</v>
+        <v>14.5</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -66655,19 +66857,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>14.03</v>
+        <v>14.49</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -66676,61 +66878,61 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>13.887</v>
+        <v>14</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>13.686</v>
+        <v>13.887</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -66739,19 +66941,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>13.56</v>
+        <v>13.686</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -66760,19 +66962,19 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>12.818</v>
+        <v>13.56</v>
       </c>
       <c r="E123" t="n">
         <v>1</v>
@@ -66781,19 +66983,19 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>12.818</v>
       </c>
       <c r="E124" t="n">
         <v>1</v>
@@ -66807,14 +67009,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>11.583</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="n">
         <v>1</v>
@@ -66823,19 +67025,19 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>11.45</v>
+        <v>11.583</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
@@ -66844,61 +67046,61 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>10.263</v>
+        <v>11.45</v>
       </c>
       <c r="E127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
-        <v>9.199999999999999</v>
+        <v>10.263</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>8.891999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
@@ -66907,19 +67109,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>7.2</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -66928,19 +67130,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E131" t="n">
         <v>1</v>
@@ -66954,7 +67156,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -66970,19 +67172,19 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="E133" t="n">
         <v>1</v>
@@ -66991,19 +67193,19 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C134" t="n">
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>6.7</v>
+        <v>6.86</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -67017,14 +67219,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>6.562</v>
+        <v>6.7</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -67033,49 +67235,49 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>5.914000000000001</v>
+        <v>6.562</v>
       </c>
       <c r="E136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
-        <v>5</v>
+        <v>5.914000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -67087,7 +67289,7 @@
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -67096,19 +67298,19 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Genova</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E139" t="n">
         <v>1</v>
@@ -67117,19 +67319,19 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Genova</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E140" t="n">
         <v>1</v>
@@ -67138,61 +67340,61 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
         <v>2</v>
       </c>
-      <c r="D141" t="n">
-        <v>1.32</v>
-      </c>
       <c r="E141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bergamo</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>1.32</v>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Livorno</t>
-        </is>
-      </c>
       <c r="C143" t="n">
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
         <v>1</v>
@@ -67201,19 +67403,19 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>0.93</v>
+        <v>0.998</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -67222,21 +67424,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>Bergamo</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Lucca</t>
         </is>
       </c>
-      <c r="C145" t="n">
-        <v>1</v>
-      </c>
-      <c r="D145" t="n">
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
         <v>0.5</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E146" t="n">
         <v>1</v>
       </c>
     </row>
@@ -67273,7 +67496,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3">
@@ -67283,7 +67506,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13530.9435</v>
+        <v>13586.8835</v>
       </c>
     </row>
     <row r="4">
@@ -67303,7 +67526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -67875,169 +68098,169 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Terni</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Umbria</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>146.807</v>
+        <v>152.03</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Terni</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Umbria</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>142.5</v>
+        <v>146.807</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>140.88</v>
+        <v>142.5</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>134.809</v>
+        <v>140.88</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>115.921</v>
+        <v>134.809</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>102.693</v>
+        <v>115.921</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>102.054</v>
+        <v>102.693</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>96.09</v>
+        <v>102.054</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -68851,13 +69074,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>160.952</v>
+        <v>216.892</v>
       </c>
     </row>
     <row r="9">

--- a/output/Mappa_progetti_clienti_filiali.xlsx
+++ b/output/Mappa_progetti_clienti_filiali.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U318"/>
+  <dimension ref="A1:U319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26982,12 +26982,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -26997,73 +26997,73 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>PV Cutro</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Cutro</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J264" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA NAZIONALE SNC</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CUTRO</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>88842</t>
         </is>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
@@ -27083,12 +27083,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -27098,22 +27098,22 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>PV Ospedaletto Lodigiano</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Lodi</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Ospedaletto Lodigiano</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -27123,53 +27123,53 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>19.191</v>
+        <v>7</v>
       </c>
       <c r="K265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>PIAZZA CARLO MIRABELLO 2</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T265" t="inlineStr">
@@ -27184,12 +27184,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -27199,7 +27199,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>PV Bovisio Masciago</t>
+          <t>PV Ospedaletto Lodigiano</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -27209,12 +27209,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Monza e della Brianza</t>
+          <t>Lodi</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Bovisio-Masciago</t>
+          <t>Ospedaletto Lodigiano</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -27224,11 +27224,11 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="J266" t="n">
-        <v>7.2</v>
+        <v>19.191</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -27285,12 +27285,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Solaro</t>
+          <t>PV Bovisio Masciago</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -27310,12 +27310,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Monza e della Brianza</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Solaro</t>
+          <t>Bovisio-Masciago</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -27329,7 +27329,7 @@
         </is>
       </c>
       <c r="J267" t="n">
-        <v>12.818</v>
+        <v>7.2</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -27346,7 +27346,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>VIALE DON LUIGI STURZO 43</t>
+          <t>PIAZZA CARLO MIRABELLO 2</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -27356,7 +27356,7 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
@@ -27366,12 +27366,12 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T267" t="inlineStr">
@@ -27386,12 +27386,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -27401,7 +27401,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>Solaro</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Solaro</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -27426,11 +27426,11 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J268" t="n">
-        <v>67.84</v>
+        <v>12.818</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -27447,7 +27447,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIALE DON LUIGI STURZO 43</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -27457,7 +27457,7 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
@@ -27467,7 +27467,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
@@ -27487,12 +27487,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>PV Cerro Maggiore</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Cerro Maggiore</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>12.364</v>
+        <v>67.84</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -27548,7 +27548,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>VIA LEONE XIII 14</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
@@ -27588,12 +27588,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -27603,7 +27603,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>PIEVE ALBIGNOLA</t>
+          <t>PV Cerro Maggiore</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -27613,12 +27613,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Pieve Albignola</t>
+          <t>Cerro Maggiore</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -27628,11 +27628,11 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J270" t="n">
-        <v>40.31</v>
+        <v>12.364</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -27649,32 +27649,32 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>VIA LEONE XIII 14</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T270" t="inlineStr">
@@ -27689,12 +27689,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PIEVE ALBIGNOLA</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -27719,7 +27719,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Pieve Albignola</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -27733,7 +27733,7 @@
         </is>
       </c>
       <c r="J271" t="n">
-        <v>14.528</v>
+        <v>40.31</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -27750,32 +27750,32 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T271" t="inlineStr">
@@ -27790,12 +27790,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Scaldasole 41</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Scaldasole</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -27834,7 +27834,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>37.16</v>
+        <v>14.528</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -27851,17 +27851,17 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
@@ -27891,12 +27891,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -27906,22 +27906,22 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>PV Alessandria</t>
+          <t>Scaldasole 41</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Scaldasole</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>5</v>
+        <v>37.16</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -27947,37 +27947,37 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>VIA CLAUDIO BEAUMONT 7</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T273" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>PV Tortona</t>
+          <t>PV Alessandria</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Tortona</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -28036,7 +28036,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -28093,12 +28093,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -28108,22 +28108,22 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>PV Bissina</t>
+          <t>PV Tortona</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Santa Cristina e Bissone</t>
+          <t>Tortona</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -28137,7 +28137,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>78.46299999999999</v>
+        <v>10</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -28154,32 +28154,32 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIA CLAUDIO BEAUMONT 7</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T275" t="inlineStr">
@@ -28194,12 +28194,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Cascina Grande</t>
+          <t>PV Bissina</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Dorno</t>
+          <t>Santa Cristina e Bissone</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -28238,7 +28238,7 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>121.697</v>
+        <v>78.46299999999999</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -28255,32 +28255,32 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>VIA GIOSUE' CARDUCCI 8</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>TRIESTE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T276" t="inlineStr">
@@ -28295,12 +28295,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -28310,22 +28310,22 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Spinetta Marengo PV</t>
+          <t>Cascina Grande</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alessandria</t>
+          <t>Dorno</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -28339,7 +28339,7 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>11.8</v>
+        <v>121.697</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -28356,27 +28356,27 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>VIALE REGINA MARGHERITA, 125</t>
+          <t>VIA GIOSUE' CARDUCCI 8</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TRIESTE</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
@@ -28396,12 +28396,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -28411,36 +28411,36 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>SANT’URBANO PV</t>
+          <t>Spinetta Marengo PV</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Sant'Urbano</t>
+          <t>Alessandria</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J278" t="n">
-        <v>48.5</v>
+        <v>11.8</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -28457,27 +28457,27 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIALE REGINA MARGHERITA, 125</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ORIGINI SOLAR</t>
+          <t>SANT’URBANO PV</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -28522,12 +28522,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>San Bellino</t>
+          <t>Sant'Urbano</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -28541,7 +28541,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>73.7</v>
+        <v>48.5</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -28598,12 +28598,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>PV FRASSINELLE POLESINE</t>
+          <t>ORIGINI SOLAR</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -28628,7 +28628,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Frassinelle Polesine</t>
+          <t>San Bellino</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -28642,7 +28642,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -28659,17 +28659,17 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q280" t="inlineStr">
@@ -28679,7 +28679,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
@@ -28699,12 +28699,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>PV FRASSINELLE POLESINE</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -28729,7 +28729,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Lendinara</t>
+          <t>Frassinelle Polesine</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -28743,7 +28743,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>36.32</v>
+        <v>84.3</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -28760,27 +28760,27 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S281" t="inlineStr">
@@ -28800,12 +28800,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -28815,7 +28815,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>PV Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -28830,7 +28830,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Canaro</t>
+          <t>Lendinara</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -28844,7 +28844,7 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>29.73</v>
+        <v>36.32</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -28861,27 +28861,27 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>VIA DEI PELLEGRINI 22</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
@@ -28901,12 +28901,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -28916,7 +28916,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>PV Villadose</t>
+          <t>PV Canaro</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Villadose</t>
+          <t>Canaro</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -28945,7 +28945,7 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>37.481</v>
+        <v>29.73</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -28962,32 +28962,32 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+          <t>VIA DEI PELLEGRINI 22</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -29002,12 +29002,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -29017,7 +29017,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>CASTELNOVO B.</t>
+          <t>PV Villadose</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -29032,7 +29032,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Castelnovo Bariano</t>
+          <t>Villadose</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -29046,7 +29046,7 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>15.03</v>
+        <v>37.481</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -29063,32 +29063,32 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>VIA VARESE 194</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
@@ -29103,12 +29103,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Bagnoli 1, 2, 3, 4</t>
+          <t>CASTELNOVO B.</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -29128,26 +29128,26 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
+          <t>Rovigo</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Castelnovo Bariano</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
           <t>Padova</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>Bagnoli di Sopra</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>Padova</t>
-        </is>
-      </c>
       <c r="J285" t="n">
-        <v>26.67</v>
+        <v>15.03</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -29164,7 +29164,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>VIA VARESE 194</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -29174,7 +29174,7 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -29204,12 +29204,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>PV via Murazze snc</t>
+          <t>Bagnoli 1, 2, 3, 4</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -29229,12 +29229,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Porto Viro</t>
+          <t>Bagnoli di Sopra</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -29248,7 +29248,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>19.56</v>
+        <v>26.67</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -29305,12 +29305,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -29320,7 +29320,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>PV Ariano nel Polese</t>
+          <t>PV via Murazze snc</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -29335,7 +29335,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Ariano nel Polesine</t>
+          <t>Porto Viro</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -29349,7 +29349,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>19.09</v>
+        <v>19.56</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>VIA GIANFRANCO MALIPIERO 16-18</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -29376,7 +29376,7 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q287" t="inlineStr">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S287" t="inlineStr">
@@ -29406,12 +29406,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>PV Stienta</t>
+          <t>PV Ariano nel Polese</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Stienta</t>
+          <t>Ariano nel Polesine</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -29450,7 +29450,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>117.9</v>
+        <v>19.09</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -29467,7 +29467,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>VIA FELICE CAVALLOTTI 13</t>
+          <t>VIA GIANFRANCO MALIPIERO 16-18</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -29477,7 +29477,7 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="Q288" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
@@ -29507,12 +29507,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>PV Guarda Veneta</t>
+          <t>PV Stienta</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -29537,7 +29537,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Guarda Veneta</t>
+          <t>Stienta</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -29551,7 +29551,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>32.008</v>
+        <v>117.9</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -29568,7 +29568,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>PIAZZALE LUIGI CADORNA 6</t>
+          <t>VIA FELICE CAVALLOTTI 13</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -29578,7 +29578,7 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="Q289" t="inlineStr">
@@ -29608,12 +29608,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -29623,7 +29623,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>PV Costa di Rovigo</t>
+          <t>PV Guarda Veneta</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -29638,7 +29638,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Costa di Rovigo</t>
+          <t>Guarda Veneta</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>58.917</v>
+        <v>32.008</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -29669,32 +29669,32 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+          <t>PIAZZALE LUIGI CADORNA 6</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -29709,12 +29709,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -29724,7 +29724,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>PV Rovigo</t>
+          <t>PV Costa di Rovigo</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -29739,7 +29739,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Costa di Rovigo</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -29753,7 +29753,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>48.57</v>
+        <v>58.917</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -29770,32 +29770,32 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>VIA SANTA MARIA SEGRETA 6</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -29810,12 +29810,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -29825,7 +29825,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Melara</t>
+          <t>PV Rovigo</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -29840,7 +29840,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Melara</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -29854,7 +29854,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>266.618</v>
+        <v>48.57</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -29871,7 +29871,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>VIA FABIO FILZI 7</t>
+          <t>VIA SANTA MARIA SEGRETA 6</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -29881,7 +29881,7 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q292" t="inlineStr">
@@ -29891,7 +29891,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S292" t="inlineStr">
@@ -29911,12 +29911,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -29926,73 +29926,73 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>PV Scotta Piacenza</t>
+          <t>Melara</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Podenzano</t>
+          <t>Melara</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J293" t="n">
-        <v>7</v>
+        <v>266.618</v>
       </c>
       <c r="K293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>VIA MONVISO 41</t>
+          <t>VIA FABIO FILZI 7</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>VILLAFALLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S293" t="inlineStr">
@@ -30012,12 +30012,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -30027,7 +30027,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Borgazzo</t>
+          <t>PV Scotta Piacenza</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -30037,63 +30037,63 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Podenzano</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J294" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>VIALE THOMAS ALVA EDISON 110</t>
+          <t>VIA MONVISO 41</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>SESTO SAN GIOVANNI</t>
+          <t>VILLAFALLETTO</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S294" t="inlineStr">
@@ -30113,12 +30113,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -30128,7 +30128,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>FABBRICO</t>
+          <t>Borgazzo</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Reggio nell'Emilia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Fabbrico</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -30157,7 +30157,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>16.806</v>
+        <v>72</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -30174,27 +30174,27 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>VIA ANTONIO ANDREUZZI 12</t>
+          <t>VIALE THOMAS ALVA EDISON 110</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>UDINE</t>
+          <t>SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
@@ -30214,12 +30214,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -30229,7 +30229,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>FABBRICO</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Montecchio Emilia</t>
+          <t>Fabbrico</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -30258,7 +30258,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>20</v>
+        <v>16.806</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -30270,32 +30270,32 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>VIA FERSINA 23</t>
+          <t>VIA ANTONIO ANDREUZZI 12</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>TRENTO</t>
+          <t>UDINE</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -30315,12 +30315,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -30330,7 +30330,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Casella</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -30340,12 +30340,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Piacenza</t>
+          <t>Reggio nell'Emilia</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Castel San Giovanni</t>
+          <t>Montecchio Emilia</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -30359,7 +30359,7 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>14.49</v>
+        <v>20</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
@@ -30371,32 +30371,32 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>PIAZZA BORROMEO 14</t>
+          <t>VIA FERSINA 23</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TRENTO</t>
         </is>
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
@@ -30416,12 +30416,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -30431,7 +30431,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Noceto</t>
+          <t>Casella</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -30441,26 +30441,26 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
+          <t>Piacenza</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Castel San Giovanni</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Noceto</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
       <c r="J298" t="n">
-        <v>15.336</v>
+        <v>14.49</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -30477,27 +30477,27 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>VIA DEL PLEBISCITO 112</t>
+          <t>PIAZZA BORROMEO 14</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
@@ -30517,12 +30517,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -30532,36 +30532,36 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Sterpara 1</t>
+          <t>Noceto</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Potenza</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Noceto</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="J299" t="n">
-        <v>19.88</v>
+        <v>15.336</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -30578,7 +30578,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA DEL PLEBISCITO 112</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -30588,7 +30588,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
@@ -30598,7 +30598,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
@@ -30618,12 +30618,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -30633,7 +30633,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>La Sterpara</t>
+          <t>Sterpara 1</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -30662,7 +30662,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>19.96</v>
+        <v>19.88</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -30679,27 +30679,27 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 60</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
@@ -30719,12 +30719,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -30734,7 +30734,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Melfi 7</t>
+          <t>La Sterpara</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -30749,7 +30749,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Melfi</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -30763,7 +30763,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>22.925</v>
+        <v>19.96</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -30780,27 +30780,27 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>VIA LUIGI BUZZI 6</t>
+          <t>FORO BUONAPARTE 60</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
@@ -30820,12 +30820,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -30835,7 +30835,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Casalini</t>
+          <t>Melfi 7</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -30850,7 +30850,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Palazzo San Gervasio</t>
+          <t>Melfi</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -30864,7 +30864,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>19.968</v>
+        <v>22.925</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -30881,27 +30881,27 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>VIA ANTONIO GRAMSCI 6</t>
+          <t>VIA LUIGI BUZZI 6</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>BUSTO GAROLFO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -30921,12 +30921,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -30936,7 +30936,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Solagna Soprana</t>
+          <t>Casalini</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Montemilone</t>
+          <t>Palazzo San Gervasio</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -30965,7 +30965,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>19.96</v>
+        <v>19.968</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -30982,27 +30982,27 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>VIA TEVERE 41</t>
+          <t>VIA ANTONIO GRAMSCI 6</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>BUSTO GAROLFO</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -31022,12 +31022,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -31037,73 +31037,73 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>PV Rubiasco</t>
+          <t>Solagna Soprana</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Potenza</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Montemilone</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Salerno</t>
         </is>
       </c>
       <c r="J304" t="n">
-        <v>12</v>
+        <v>19.96</v>
       </c>
       <c r="K304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>VIA MATTATOIO 3</t>
+          <t>VIA TEVERE 41</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>SALUZZO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -31123,12 +31123,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -31138,7 +31138,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Fattoria Solare Paradiso</t>
+          <t>PV Rubiasco</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -31153,7 +31153,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Poirino</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -31167,44 +31167,44 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>46.7235</v>
+        <v>12</v>
       </c>
       <c r="K305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>FORO BUONAPARTE 31</t>
+          <t>VIA MATTATOIO 3</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SALUZZO</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
@@ -31224,12 +31224,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -31239,7 +31239,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>PV Pinerolo</t>
+          <t>Fattoria Solare Paradiso</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -31254,7 +31254,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Pinerolo</t>
+          <t>Poirino</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -31268,7 +31268,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>2</v>
+        <v>46.7235</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -31285,27 +31285,27 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>STRADA STATALE 28 SUD 14</t>
+          <t>FORO BUONAPARTE 31</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>MONDOVI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S306" t="inlineStr">
@@ -31325,12 +31325,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -31340,7 +31340,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
+          <t>PV Pinerolo</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Lombardore</t>
+          <t>Pinerolo</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -31369,7 +31369,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>18.774</v>
+        <v>2</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -31386,27 +31386,27 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>VIA SENATO 28</t>
+          <t>STRADA STATALE 28 SUD 14</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONDOVI</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S307" t="inlineStr">
@@ -31426,12 +31426,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -31441,7 +31441,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>PV Maserano</t>
+          <t>Lombardore 1 - Lombardore 2 - San Benigno 1</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -31451,12 +31451,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Biella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Masserano</t>
+          <t>Lombardore</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -31470,10 +31470,10 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>18</v>
+        <v>18.774</v>
       </c>
       <c r="K308" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -31482,32 +31482,32 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>VIA VARALLO POMBIA 44</t>
+          <t>VIA SENATO 28</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>CASTELLETTO SOPRA TICINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -31527,12 +31527,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -31542,39 +31542,39 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Maniago Solar 1- ELLO 11</t>
+          <t>PV Maserano</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Biella</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Maniago</t>
+          <t>Masserano</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>96.09</v>
+        <v>18</v>
       </c>
       <c r="K309" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -31583,32 +31583,32 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>VIA SEBASTIAN ALTMANN 9</t>
+          <t>VIA VARALLO POMBIA 44</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>BOLZANO</t>
+          <t>CASTELLETTO SOPRA TICINO</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
@@ -31628,12 +31628,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -31643,7 +31643,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>GREENFRUT</t>
+          <t>Maniago Solar 1- ELLO 11</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -31653,26 +31653,26 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
+          <t>Pordenone</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Maniago</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Nord Est</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
           <t>Udine</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>Bicinicco</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>Nord Est</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>Udine</t>
-        </is>
-      </c>
       <c r="J310" t="n">
-        <v>68.51000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -31689,32 +31689,32 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+          <t>VIA SEBASTIAN ALTMANN 9</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>BICINICCO</t>
+          <t>BOLZANO</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T310" t="inlineStr">
@@ -31729,12 +31729,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -31744,7 +31744,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>PV Sesto al Reghena</t>
+          <t>GREENFRUT</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -31754,12 +31754,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Pordenone</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Sesto al Reghena</t>
+          <t>Bicinicco</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -31773,7 +31773,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>55.94</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -31790,32 +31790,32 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>VIA CARAVAGGIO 125</t>
+          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>PESCARA</t>
+          <t>BICINICCO</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>33050</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>UD</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T311" t="inlineStr">
@@ -31830,12 +31830,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -31845,22 +31845,22 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>PV PORTOGRUARO</t>
+          <t>PV Sesto al Reghena</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pordenone</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Portogruaro</t>
+          <t>Sesto al Reghena</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -31870,11 +31870,11 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>20.787</v>
+        <v>55.94</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -31891,27 +31891,27 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
+          <t>VIA CARAVAGGIO 125</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>65125</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -31931,12 +31931,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -31946,7 +31946,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Cona 1/2/3/4/5</t>
+          <t>PV PORTOGRUARO</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -31961,7 +31961,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Cona</t>
+          <t>Portogruaro</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -31975,7 +31975,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>27.867</v>
+        <v>20.787</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -31992,27 +31992,27 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>VIA BIGLI 2</t>
+          <t>LUNGO PO ALESSANDRO ANTONELLI 21</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="S313" t="inlineStr">
@@ -32032,12 +32032,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -32047,7 +32047,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>PV Cavarzere</t>
+          <t>Cona 1/2/3/4/5</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Cavarzere</t>
+          <t>Cona</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -32076,7 +32076,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>53.4</v>
+        <v>27.867</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -32093,27 +32093,27 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>PIAZZA CAVOUR 17</t>
+          <t>VIA BIGLI 2</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S314" t="inlineStr">
@@ -32133,12 +32133,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -32148,36 +32148,36 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>PV Cavarzere</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Cavarzere</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="J315" t="n">
-        <v>18.419</v>
+        <v>53.4</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -32194,32 +32194,32 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>VIA ALDO MORO 233</t>
+          <t>PIAZZA CAVOUR 17</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>FROSINONE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>STESSA FILIALE</t>
+          <t>FILIALE DIVERSA</t>
         </is>
       </c>
       <c r="T315" t="inlineStr">
@@ -32234,12 +32234,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -32249,7 +32249,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Latina Fondazione</t>
+          <t>EGPM-FV082</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -32264,7 +32264,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pontinia</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -32278,7 +32278,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>28.61</v>
+        <v>18.419</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -32295,32 +32295,32 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>PIAZZA CASTELLO 19</t>
+          <t>VIA ALDO MORO 233</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FROSINONE</t>
         </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>FILIALE DIVERSA</t>
+          <t>STESSA FILIALE</t>
         </is>
       </c>
       <c r="T316" t="inlineStr">
@@ -32335,12 +32335,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -32350,7 +32350,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Prato Smeraldo</t>
+          <t>Latina Fondazione</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -32365,7 +32365,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -32379,7 +32379,7 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>8.891999999999999</v>
+        <v>28.61</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -32396,27 +32396,27 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>VIALE CASTRENSE 9</t>
+          <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -32436,12 +32436,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>SOLAR PV 1 SRL</t>
+          <t>RAI WAY SPA</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>PV Paliano</t>
+          <t>Prato Smeraldo</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -32461,26 +32461,26 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>Paliano</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>Sud</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
       <c r="J318" t="n">
-        <v>38.99</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -32497,40 +32497,141 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
+          <t>VIALE CASTRENSE 9</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>FILIALE DIVERSA</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>PV Paliano</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Paliano</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="K319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
           <t>PIAZZA CASTELLO 19</t>
         </is>
       </c>
-      <c r="O318" t="inlineStr">
+      <c r="O319" t="inlineStr">
         <is>
           <t>MILANO</t>
         </is>
       </c>
-      <c r="P318" t="inlineStr">
+      <c r="P319" t="inlineStr">
         <is>
           <t>20121</t>
         </is>
       </c>
-      <c r="Q318" t="inlineStr">
+      <c r="Q319" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="R318" t="inlineStr">
+      <c r="R319" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>
       </c>
-      <c r="S318" t="inlineStr">
+      <c r="S319" t="inlineStr">
         <is>
           <t>FILIALE DIVERSA</t>
         </is>
       </c>
-      <c r="T318" t="inlineStr">
+      <c r="T319" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U318" t="n">
+      <c r="U319" t="n">
         <v>1</v>
       </c>
     </row>
@@ -60740,7 +60841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63673,12 +63774,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -63688,73 +63789,73 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PV Virle Piemonte</t>
+          <t>PV Cutro</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Virle Piemonte</t>
+          <t>Cutro</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nord Ovest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Attivo</t>
+          <t>In pipeline</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Costruzione</t>
+          <t>Autorizzazioni</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>VIA APPIA NUOVA 41</t>
+          <t>VIA NAZIONALE SNC</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CUTRO</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>88842</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -63774,12 +63875,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -63789,22 +63890,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Solaro</t>
+          <t>PV Virle Piemonte</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Milano</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Solaro</t>
+          <t>Virle Piemonte</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -63814,48 +63915,48 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>12.818</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>In pipeline</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Autorizzazioni</t>
+          <t>Costruzione</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>VIALE DON LUIGI STURZO 43</t>
+          <t>VIA APPIA NUOVA 41</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -63875,12 +63976,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -63890,7 +63991,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ranteghetta</t>
+          <t>Solaro</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -63905,7 +64006,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Marcallo con Casone</t>
+          <t>Solaro</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -63915,11 +64016,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>67.84</v>
+        <v>12.818</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -63936,7 +64037,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>VIA ALESSANDRO ALGARDI 4</t>
+          <t>VIALE DON LUIGI STURZO 43</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -63946,7 +64047,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -63956,7 +64057,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -63976,12 +64077,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -63991,7 +64092,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PV Cerro Maggiore</t>
+          <t>Ranteghetta</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -64006,7 +64107,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cerro Maggiore</t>
+          <t>Marcallo con Casone</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -64020,7 +64121,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>12.364</v>
+        <v>67.84</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -64037,7 +64138,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>VIA LEONE XIII 14</t>
+          <t>VIA ALESSANDRO ALGARDI 4</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -64047,7 +64148,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -64077,12 +64178,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -64092,7 +64193,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PV Cura Carpignano</t>
+          <t>PV Cerro Maggiore</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -64102,12 +64203,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pavia</t>
+          <t>Milano</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cura Carpignano</t>
+          <t>Cerro Maggiore</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -64117,11 +64218,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>14.528</v>
+        <v>12.364</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -64138,17 +64239,17 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
+          <t>VIA LEONE XIII 14</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>ROZZANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -64158,7 +64259,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -64178,12 +64279,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -64193,7 +64294,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Scaldasole 41</t>
+          <t>PV Cura Carpignano</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -64208,7 +64309,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scaldasole</t>
+          <t>Cura Carpignano</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -64222,7 +64323,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>37.16</v>
+        <v>14.528</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -64239,17 +64340,17 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>VIA GAETANO NEGRI 4</t>
+          <t>STRADA 4 PALAZZO Q 8 MILANOFIORI</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROZZANO</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -64279,12 +64380,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -64294,7 +64395,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PV Bissina</t>
+          <t>Scaldasole 41</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -64309,7 +64410,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Santa Cristina e Bissone</t>
+          <t>Scaldasole</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -64323,7 +64424,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>78.46299999999999</v>
+        <v>37.16</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -64340,7 +64441,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>LARGO GUIDO DONEGANI 2</t>
+          <t>VIA GAETANO NEGRI 4</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -64350,7 +64451,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -64380,12 +64481,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -64395,36 +64496,36 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PV Villadose</t>
+          <t>PV Bissina</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rovigo</t>
+          <t>Pavia</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Villadose</t>
+          <t>Santa Cristina e Bissone</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nord Est</t>
+          <t>Nord Ovest</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>37.481</v>
+        <v>78.46299999999999</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -64441,27 +64542,27 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
+          <t>LARGO GUIDO DONEGANI 2</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -64481,12 +64582,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -64496,7 +64597,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PV Costa di Rovigo</t>
+          <t>PV Villadose</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -64511,7 +64612,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Costa di Rovigo</t>
+          <t>Villadose</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -64525,7 +64626,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>58.917</v>
+        <v>37.481</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -64582,12 +64683,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -64597,22 +64698,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GREENFRUT</t>
+          <t>PV Costa di Rovigo</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Friuli-Venezia Giulia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Rovigo</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bicinicco</t>
+          <t>Costa di Rovigo</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -64622,11 +64723,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>68.51000000000001</v>
+        <v>58.917</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -64643,27 +64744,27 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+          <t>VIALE COMBATTENTI ALLEATI D'EUROPA 9/G</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>BICINICCO</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>UD</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -64683,12 +64784,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -64698,36 +64799,36 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EGPM-FV082</t>
+          <t>GREENFRUT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Friuli-Venezia Giulia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pontinia</t>
+          <t>Bicinicco</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord Est</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>18.419</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -64744,40 +64845,141 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
+          <t>STRADA PROVINCIALE N. 82 DI CHIASIELLIS</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>BICINICCO</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>33050</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>UD</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>STESSA FILIALE</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EGPM-FV082</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pontinia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sud</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>18.419</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>In pipeline</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Autorizzazioni</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>VIA ALDO MORO 233</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>FROSINONE</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>STESSA FILIALE</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
-      <c r="U40" t="n">
+      <c r="U41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -64792,7 +64994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67492,19 +67694,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
@@ -67513,19 +67715,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>8.891999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -67534,19 +67736,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>7.2</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="E131" t="n">
         <v>1</v>
@@ -67555,19 +67757,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -67581,7 +67783,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -67597,19 +67799,19 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="C134" t="n">
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -67618,19 +67820,19 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Brescia</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lucca</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>6.7</v>
+        <v>6.86</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -67644,14 +67846,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>6.562</v>
+        <v>6.7</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -67660,49 +67862,49 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>5.914000000000001</v>
+        <v>6.562</v>
       </c>
       <c r="E137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
-        <v>5</v>
+        <v>5.914000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -67714,7 +67916,7 @@
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="E139" t="n">
         <v>1</v>
@@ -67723,19 +67925,19 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Genova</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E140" t="n">
         <v>1</v>
@@ -67744,19 +67946,19 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Genova</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
@@ -67765,61 +67967,61 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Cuneo</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
         <v>2</v>
       </c>
-      <c r="D142" t="n">
-        <v>1.32</v>
-      </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bergamo</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>1.32</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Livorno</t>
-        </is>
-      </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -67828,19 +68030,19 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="C145" t="n">
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>0.93</v>
+        <v>0.998</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
@@ -67849,21 +68051,42 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
           <t>Bergamo</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Lucca</t>
         </is>
       </c>
-      <c r="C146" t="n">
-        <v>1</v>
-      </c>
-      <c r="D146" t="n">
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
         <v>0.5</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -67900,7 +68123,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3">
@@ -67910,7 +68133,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13700.8525</v>
+        <v>13710.6525</v>
       </c>
     </row>
     <row r="4">
@@ -67920,7 +68143,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -68985,61 +69208,61 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>45.545</v>
+        <v>47.026</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>38.99</v>
+        <v>45.545</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>38.16</v>
+        <v>38.99</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -69048,22 +69271,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>37.226</v>
+        <v>38.16</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -69350,7 +69573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70030,7 +70253,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -70040,13 +70263,13 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>3.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -70056,22 +70279,38 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.998</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>LI</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
         <v>0.514</v>
       </c>
     </row>
